--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486946_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486946_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4825</v>
+        <v>4.1069</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1696</v>
+        <v>6.8829</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.6871</v>
+        <v>-2.7761</v>
       </c>
       <c r="G2" t="n">
         <v>3.302</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7698</v>
+        <v>0.3942</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5384</v>
+        <v>0.2517</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2314</v>
+        <v>0.1425</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5511</v>
+        <v>1.3384</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6</v>
+        <v>3.1501</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0489</v>
+        <v>-1.8117</v>
       </c>
       <c r="G3" t="n">
         <v>1.4392</v>
@@ -688,13 +688,13 @@
         <v>1.2321</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6745</v>
+        <v>-0.8872</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8563</v>
+        <v>-0.3062</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8182</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2402</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1443</v>
+        <v>0.2036</v>
       </c>
       <c r="E4" t="n">
         <v>-0.7243000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8686</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1005</v>
@@ -766,13 +766,13 @@
         <v>0.4107</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1658</v>
+        <v>-0.1065</v>
       </c>
       <c r="T4" t="n">
         <v>-0.0659</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0999</v>
+        <v>-0.0407</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2737</v>
+        <v>-0.6633</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.2462</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2095</v>
+        <v>-0.417</v>
       </c>
       <c r="G5" t="n">
         <v>1.264</v>
@@ -844,13 +844,13 @@
         <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6676</v>
+        <v>0.278</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2362</v>
+        <v>0.0542</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4313</v>
+        <v>0.2238</v>
       </c>
       <c r="V5" t="n">
         <v>-1.1786</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ALVAREZ PUERTAS</t>
+          <t>G. MULERO MALDONADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8293</v>
+        <v>-0.7958</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0409</v>
+        <v>2.3893</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8702</v>
+        <v>-3.1851</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.4755</v>
+        <v>0.6997</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4216</v>
+        <v>-0.1555</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.8971</v>
+        <v>0.8552</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4239</v>
+        <v>5.3921</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9183</v>
+        <v>1.5904</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3422</v>
+        <v>3.8017</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0516</v>
+        <v>-4.6924</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4967</v>
+        <v>-1.7459</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.5549</v>
+        <v>-2.9465</v>
       </c>
       <c r="P6" t="n">
-        <v>0.616</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2053</v>
+        <v>-3.0801</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0301</v>
+        <v>-0.2984</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6701</v>
+        <v>-0.1629</v>
       </c>
       <c r="U6" t="n">
-        <v>0.36</v>
+        <v>-0.1354</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. MULERO MALDONADO</t>
+          <t>M. ALVAREZ PUERTAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2661</v>
+        <v>-1.2502</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8004</v>
+        <v>-0.3504</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.0666</v>
+        <v>-0.8998</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6997</v>
+        <v>-2.4755</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1555</v>
+        <v>0.4216</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8552</v>
+        <v>-2.8971</v>
       </c>
       <c r="J7" t="n">
-        <v>5.3921</v>
+        <v>-0.4239</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5904</v>
+        <v>0.9183</v>
       </c>
       <c r="L7" t="n">
-        <v>3.8017</v>
+        <v>-1.3422</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.6924</v>
+        <v>-2.0516</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7459</v>
+        <v>-0.4967</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.9465</v>
+        <v>-1.5549</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.4374</v>
+        <v>0.616</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0801</v>
+        <v>-0.2053</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7687</v>
+        <v>0.6092</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7518</v>
+        <v>0.2788</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0168</v>
+        <v>0.3304</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6613</v>
+        <v>-1.5205</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3323</v>
+        <v>-0.1619</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3289</v>
+        <v>-1.3586</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0131</v>
@@ -1078,13 +1078,13 @@
         <v>0.616</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0856</v>
+        <v>0.0552</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3952</v>
+        <v>-0.2248</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3096</v>
+        <v>0.28</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1786</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7116</v>
+        <v>-1.5634</v>
       </c>
       <c r="E9" t="n">
         <v>-1.2953</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4163</v>
+        <v>-0.2681</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5155</v>
@@ -1156,13 +1156,13 @@
         <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1879</v>
+        <v>0.3361</v>
       </c>
       <c r="T9" t="n">
         <v>0.368</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1801</v>
+        <v>-0.0319</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MONTERO ISLA</t>
+          <t>E. ORTIZ TORRES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2793</v>
+        <v>-4.1087</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8464</v>
+        <v>-1.266</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4329</v>
+        <v>-2.8427</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.1215</v>
+        <v>-2.3213</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.4215</v>
+        <v>-0.6584</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>-1.6629</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7258</v>
+        <v>-0.5143</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.37</v>
+        <v>-0.3825</v>
       </c>
       <c r="L10" t="n">
-        <v>2.6442</v>
+        <v>-0.1318</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.3958</v>
+        <v>-1.8071</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0516</v>
+        <v>-0.2759</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.3442</v>
+        <v>-1.5311</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2321</v>
+        <v>-0.616</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6917</v>
+        <v>0.5966</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4225</v>
+        <v>0.4803</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2692</v>
+        <v>0.1163</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6982</v>
+        <v>-1.7679</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>A. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7844</v>
+        <v>-4.1698</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8504</v>
+        <v>-1.8851</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.934</v>
+        <v>-2.2847</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8096</v>
+        <v>-4.1215</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4182</v>
+        <v>-4.4215</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.3914</v>
+        <v>0.3</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1571</v>
+        <v>-0.7258</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5782</v>
+        <v>-3.37</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4211</v>
+        <v>2.6442</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.9667</v>
+        <v>-3.3958</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9964</v>
+        <v>-1.0516</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.9703</v>
+        <v>-2.3442</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.2855</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9205</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9064</v>
+        <v>-0.4612</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0142</v>
+        <v>-0.121</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0472</v>
+        <v>-0.6982</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3716</v>
+        <v>-0.6982</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. ORTIZ TORRES</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.419</v>
+        <v>-5.8187</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3392</v>
+        <v>-2.2029</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.0798</v>
+        <v>-3.6157</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.3213</v>
+        <v>-3.8096</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6584</v>
+        <v>-0.4182</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6629</v>
+        <v>-3.3914</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5143</v>
+        <v>0.1571</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3825</v>
+        <v>0.5782</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1318</v>
+        <v>-0.4211</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8071</v>
+        <v>-3.9667</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2759</v>
+        <v>-0.9964</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5311</v>
+        <v>-2.9703</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.616</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.2321</v>
+        <v>-3.2855</v>
       </c>
       <c r="R12" t="n">
-        <v>0.616</v>
+        <v>1.4374</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7137</v>
+        <v>0.8862</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5928</v>
+        <v>0.5538</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1208</v>
+        <v>0.3324</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7679</v>
+        <v>-1.0472</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.3716</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7679</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.9397</v>
+        <v>-6.7569</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9281</v>
+        <v>-2.0714</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.0116</v>
+        <v>-4.6856</v>
       </c>
       <c r="G13" t="n">
         <v>-6.4905</v>
@@ -1468,13 +1468,13 @@
         <v>1.0267</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6894</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.209</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8984</v>
+        <v>-0.5723</v>
       </c>
       <c r="V13" t="n">
         <v>0.2402</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-21.9865</v>
+        <v>-20.9984</v>
       </c>
       <c r="E14" t="n">
-        <v>1.230699999999999</v>
+        <v>2.218800000000002</v>
       </c>
       <c r="F14" t="n">
         <v>-23.2172</v>
@@ -1513,7 +1513,7 @@
         <v>-16.1426</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.394699999999999</v>
+        <v>-1.3947</v>
       </c>
       <c r="I14" t="n">
         <v>-14.748</v>
@@ -1537,7 +1537,7 @@
         <v>-20.5339</v>
       </c>
       <c r="P14" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>-12.3205</v>
@@ -1546,13 +1546,13 @@
         <v>12.3205</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2135</v>
+        <v>0.7746000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1564</v>
+        <v>0.8315</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.05689999999999995</v>
+        <v>-0.05699999999999994</v>
       </c>
       <c r="V14" t="n">
         <v>-5.6303</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.009499999999999</v>
+        <v>9.2606</v>
       </c>
       <c r="E15" t="n">
-        <v>8.631</v>
+        <v>8.526400000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3785</v>
+        <v>0.7342</v>
       </c>
       <c r="G15" t="n">
         <v>5.3338</v>
@@ -1624,13 +1624,13 @@
         <v>1.4374</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.4571</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0386</v>
+        <v>-0.066</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7469</v>
+        <v>-0.3912</v>
       </c>
       <c r="V15" t="n">
         <v>2.9466</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.1096</v>
+        <v>6.4687</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9215</v>
+        <v>6.3399</v>
       </c>
       <c r="F16" t="n">
-        <v>0.188</v>
+        <v>0.1288</v>
       </c>
       <c r="G16" t="n">
         <v>7.3501</v>
@@ -1702,13 +1702,13 @@
         <v>1.0267</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5547</v>
+        <v>-0.1956</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5928</v>
+        <v>-0.1744</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0381</v>
+        <v>-0.0211</v>
       </c>
       <c r="V16" t="n">
         <v>-0.4805</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8336</v>
+        <v>4.1161</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9569</v>
+        <v>2.0615</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8767</v>
+        <v>2.0546</v>
       </c>
       <c r="G17" t="n">
         <v>2.7379</v>
@@ -1780,13 +1780,13 @@
         <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1922</v>
+        <v>0.4746</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1704</v>
+        <v>0.275</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0218</v>
+        <v>0.1996</v>
       </c>
       <c r="V17" t="n">
         <v>0.6982</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.8203</v>
+        <v>3.5954</v>
       </c>
       <c r="E18" t="n">
-        <v>4.2717</v>
+        <v>3.9579</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4514</v>
+        <v>-0.3625</v>
       </c>
       <c r="G18" t="n">
         <v>1.1128</v>
@@ -1858,13 +1858,13 @@
         <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2065</v>
+        <v>-0.0184</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3098</v>
+        <v>-0.004</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1034</v>
+        <v>-0.0144</v>
       </c>
       <c r="V18" t="n">
         <v>2.7063</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.863</v>
+        <v>2.1168</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7201</v>
+        <v>1.0924</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1429</v>
+        <v>1.0244</v>
       </c>
       <c r="G19" t="n">
         <v>0.4662</v>
@@ -1936,13 +1936,13 @@
         <v>1.2321</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9245</v>
+        <v>0.1783</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6701</v>
+        <v>0.0425</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2544</v>
+        <v>0.1358</v>
       </c>
       <c r="V19" t="n">
         <v>0.2402</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.7704</v>
+        <v>1.4566</v>
       </c>
       <c r="E20" t="n">
-        <v>3.0883</v>
+        <v>2.7745</v>
       </c>
       <c r="F20" t="n">
         <v>-1.3179</v>
@@ -2014,10 +2014,10 @@
         <v>1.8481</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4843</v>
+        <v>0.1705</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4802</v>
+        <v>0.1664</v>
       </c>
       <c r="U20" t="n">
         <v>0.0041</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1237</v>
+        <v>0.0402</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2582</v>
+        <v>-0.1536</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1345</v>
+        <v>0.1938</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0314</v>
@@ -2092,13 +2092,13 @@
         <v>0.2053</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0922</v>
+        <v>0.0717</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1317</v>
+        <v>-0.0271</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0395</v>
+        <v>0.0988</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. BITJAA KODY</t>
+          <t>J. MOLINA MARTINEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7207</v>
+        <v>-0.7574</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5017</v>
+        <v>1.4588</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.219</v>
+        <v>-2.2163</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4197</v>
+        <v>0.5982</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8885999999999999</v>
+        <v>0.3955</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5311</v>
+        <v>0.2027</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6341</v>
+        <v>1.4551</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.726</v>
+        <v>0.1397</v>
       </c>
       <c r="L22" t="n">
-        <v>0.092</v>
+        <v>1.3154</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7856</v>
+        <v>-0.8569</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1626</v>
+        <v>0.2559</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6231</v>
+        <v>-1.1127</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4107</v>
+        <v>1.0267</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1097</v>
+        <v>-0.0251</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0195</v>
+        <v>0.0038</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1292</v>
+        <v>-0.0289</v>
       </c>
       <c r="V22" t="n">
-        <v>1.1786</v>
+        <v>-2.3573</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. MOLINA MARTINEZ</t>
+          <t>C. HURTADO CERVANTES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1026</v>
+        <v>-0.992</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9358</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0384</v>
+        <v>-1.6265</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5982</v>
+        <v>0.1932</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3955</v>
+        <v>-0.6616</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2027</v>
+        <v>0.8548</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4551</v>
+        <v>2.4471</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1397</v>
+        <v>0.2244</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3154</v>
+        <v>2.2227</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8569</v>
+        <v>-2.2539</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2559</v>
+        <v>-0.886</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1127</v>
+        <v>-1.3679</v>
       </c>
       <c r="P23" t="n">
-        <v>1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.2855</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3703</v>
+        <v>0.5192</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5192</v>
+        <v>0.2943</v>
       </c>
       <c r="U23" t="n">
-        <v>0.149</v>
+        <v>0.2249</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.3573</v>
+        <v>0.3491</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.3573</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C. HURTADO CERVANTES</t>
+          <t>J. BITJAA KODY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4244</v>
+        <v>-1.1374</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3208</v>
+        <v>-0.7109</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7451</v>
+        <v>-0.4265</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1932</v>
+        <v>-2.4197</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6616</v>
+        <v>-0.8885999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8548</v>
+        <v>-1.5311</v>
       </c>
       <c r="J24" t="n">
-        <v>2.4471</v>
+        <v>-0.6341</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2244</v>
+        <v>-0.726</v>
       </c>
       <c r="L24" t="n">
-        <v>2.2227</v>
+        <v>0.092</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.2539</v>
+        <v>-1.7856</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.886</v>
+        <v>-0.1626</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.3679</v>
+        <v>-1.6231</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0534</v>
+        <v>0.4107</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.2855</v>
+        <v>-1.0267</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0868</v>
+        <v>-0.307</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0195</v>
+        <v>-0.2287</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1063</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3491</v>
+        <v>1.1786</v>
       </c>
       <c r="W24" t="n">
         <v>1.1786</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.0486</v>
+        <v>-2.1811</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8691</v>
+        <v>-2.7645</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8205</v>
+        <v>0.5834</v>
       </c>
       <c r="G25" t="n">
         <v>0.3286</v>
@@ -2404,13 +2404,13 @@
         <v>0.616</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.065</v>
+        <v>-0.1975</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3294</v>
+        <v>-0.2248</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2644</v>
+        <v>0.0272</v>
       </c>
       <c r="V25" t="n">
         <v>1.1786</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>21.9864</v>
+        <v>21.9865</v>
       </c>
       <c r="E26" t="n">
-        <v>23.2171</v>
+        <v>23.217</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.230700000000001</v>
+        <v>-1.230499999999999</v>
       </c>
       <c r="G26" t="n">
         <v>16.1426</v>
@@ -2458,7 +2458,7 @@
         <v>26.7497</v>
       </c>
       <c r="K26" t="n">
-        <v>6.216100000000001</v>
+        <v>6.2161</v>
       </c>
       <c r="L26" t="n">
         <v>20.5337</v>
@@ -2467,13 +2467,13 @@
         <v>-10.6073</v>
       </c>
       <c r="N26" t="n">
-        <v>-4.8213</v>
+        <v>-4.821300000000001</v>
       </c>
       <c r="O26" t="n">
         <v>-5.786</v>
       </c>
       <c r="P26" t="n">
-        <v>9.999999999976694e-05</v>
+        <v>9.999999999932285e-05</v>
       </c>
       <c r="Q26" t="n">
         <v>-12.3205</v>
@@ -2485,13 +2485,13 @@
         <v>0.2136</v>
       </c>
       <c r="T26" t="n">
-        <v>0.057</v>
+        <v>0.05700000000000005</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1565000000000001</v>
+        <v>0.1565</v>
       </c>
       <c r="V26" t="n">
-        <v>5.630299999999999</v>
+        <v>5.6303</v>
       </c>
       <c r="W26" t="n">
         <v>8.7308</v>
